--- a/input_data/admin_data/COL/_clean/total-pre-COL-adults.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pre-COL-adults.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="11">
   <si>
     <t>poptot</t>
   </si>

--- a/input_data/admin_data/COL/_clean/total-pre-COL-adults.xlsx
+++ b/input_data/admin_data/COL/_clean/total-pre-COL-adults.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="11">
   <si>
     <t>poptot</t>
   </si>
